--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260602.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260602.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>6,420,000</t>
+          <t>16,280,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>62,740,000</t>
+          <t>6,420,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>16,280,000</t>
+          <t>62,740,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,850,000</t>
+          <t>19,910,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>19,910,000</t>
+          <t>2,850,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>26,620,000</t>
+          <t>24,530,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>24,530,000</t>
+          <t>26,620,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
